--- a/稳定性实验结果.xlsx
+++ b/稳定性实验结果.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xiuli.dong\Desktop\其他资料\东财\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{39A3767D-DEB7-4847-A8B2-4E107AF17B0A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D000033B-5EAF-42F0-A6BF-AAE971AE63C7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12015" xr2:uid="{8D0A875F-D227-4EC7-83DB-683A4AC96B50}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
   <si>
     <t>记录</t>
   </si>
@@ -166,12 +167,109 @@
     </r>
     <phoneticPr fontId="3"/>
   </si>
+  <si>
+    <t>SMOOTH防止yolo本身学习震荡导致的评价失衡补充稳定性对比实验
+标签平滑：--label_smoothing 0.1  --cos_lr</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>E2B seed1 (Append</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>E1 seed3 (V1)</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>E2A seed3 (Verifier)</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>E2B seed3 (Append</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>E1 seed4 (V1)</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>E2A seed4 (Verifier)</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>E2B seed4 (Append</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>E1 seed5 (V1)</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>E2A seed5 (Verifier)</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>E2B seed5 (Append</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -208,6 +306,13 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,6 +329,12 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
@@ -231,7 +342,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -240,7 +351,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -254,11 +383,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFDCDFE5"/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -268,35 +403,41 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -613,49 +754,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B46285A-8840-4720-B87B-F41FE3951CF4}">
-  <dimension ref="B4:F17"/>
+  <dimension ref="B4:F33"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
+    <col min="1" max="1" width="16.875" customWidth="1"/>
     <col min="2" max="2" width="27.625" customWidth="1"/>
-    <col min="5" max="5" width="9" style="4"/>
+    <col min="5" max="5" width="9" style="1"/>
     <col min="6" max="6" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="1" t="s">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B4" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="5" t="s">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="6">
         <v>0.82050000000000001</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="6">
         <v>0.67169999999999996</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="6">
         <v>0.74299999999999999</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="6">
         <v>0.53769999999999996</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
@@ -672,7 +814,7 @@
         <v>0.46229999999999999</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
@@ -689,24 +831,24 @@
         <v>0.4577</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="6" t="s">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B8" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="8">
         <v>0.71479999999999999</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="8">
         <v>0.64319999999999999</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="9">
         <v>0.67220000000000002</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="8">
         <v>0.46060000000000001</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B9" s="2" t="s">
         <v>5</v>
       </c>
@@ -723,7 +865,7 @@
         <v>0.42599999999999999</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
@@ -740,75 +882,75 @@
         <v>0.45600000000000002</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="6" t="s">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B11" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="8">
         <v>0.70340000000000003</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="8">
         <v>0.66279999999999994</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="9">
         <v>0.6603</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="8">
         <v>0.435</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="2" t="s">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B12" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="10">
         <v>0.748</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="10">
         <v>0.58599999999999997</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="10">
         <v>0.64900000000000002</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="10">
         <v>0.442</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B13" s="2" t="s">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B13" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="10">
         <v>0.69199999999999995</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="10">
         <v>0.65400000000000003</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="10">
         <v>0.66</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="10">
         <v>0.45100000000000001</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B14" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="6">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B14" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="11">
         <v>0.66579999999999995</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="11">
         <v>0.66720000000000002</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="4">
         <v>0.64800000000000002</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="11">
         <v>0.43020000000000003</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B15" s="2" t="s">
         <v>9</v>
       </c>
@@ -826,40 +968,221 @@
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="2">
         <v>0.71799999999999997</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="2">
         <v>0.63500000000000001</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="2">
         <v>0.67500000000000004</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
         <v>0.46400000000000002</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="6" t="s">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B17" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="8">
         <v>0.71650000000000003</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="8">
         <v>0.64029999999999998</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="4">
         <v>0.66490000000000005</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="8">
         <v>0.43240000000000001</v>
       </c>
     </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B18" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B19" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B20" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="11"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B21" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="11"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B22" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="11"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B23" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="8"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B24" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="8"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B25" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="8"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B26" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="8"/>
+    </row>
+    <row r="27" spans="2:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B27" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0.748</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0.58620000000000005</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0.6492</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.44209999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0.6915</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0.65410000000000001</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0.6603</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.45100000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B30" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="3">
+        <v>0.71125000000000005</v>
+      </c>
+      <c r="D30" s="3">
+        <v>0.60289999999999999</v>
+      </c>
+      <c r="E30" s="4">
+        <v>0.64939999999999998</v>
+      </c>
+      <c r="F30" s="3">
+        <v>0.43619999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="3"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B27:F27"/>
+  </mergeCells>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA96322B-8CB0-4EDC-8266-7173C8C10375}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData/>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
